--- a/GUA/IPPU/A1_Inputs/A-I_Classifier_Modes_Supply.xlsx
+++ b/GUA/IPPU/A1_Inputs/A-I_Classifier_Modes_Supply.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanc\Desktop\GUA_Modelos_Sectoriales\M0_IPPU_V2\A1_Inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IgnacioAlfaroCorrale\Desktop\Models_running\0_guatemala_2025\IPPU_GUA_v1_2025\A1_Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE525A7-253B-4D12-AD58-76B4C9326EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42F44D9-5AAE-41D9-8AD4-0677FFEDA65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="SecondaryEnergy" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">PrimaryEnergy!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">PrimaryEnergy!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="102">
   <si>
     <t>The purpose of this file is to establish a supply chain between the primary energy imports / secodnary energy production to final energy consumptions.</t>
   </si>
@@ -99,12 +99,18 @@
     <t>The *SecondaryEnergy* sheet establishes how the Seconday Energy is Distributed, conviniently.</t>
   </si>
   <si>
+    <t>Transformation</t>
+  </si>
+  <si>
     <t>Tertiary_Commodity</t>
   </si>
   <si>
     <t>Final in Chain</t>
   </si>
   <si>
+    <t>Import/Distribution</t>
+  </si>
+  <si>
     <t>YES</t>
   </si>
   <si>
@@ -135,82 +141,244 @@
     <t>Fuel - Plain Spanish (Input)</t>
   </si>
   <si>
+    <t>Raw_materials_for_clinker</t>
+  </si>
+  <si>
+    <t>Extraction</t>
+  </si>
+  <si>
     <t>RAW_MAT_CLK</t>
   </si>
   <si>
+    <t>Supply of raw material for clinker</t>
+  </si>
+  <si>
+    <t>Suministro de materia prima para clinker</t>
+  </si>
+  <si>
+    <t>Raw materials for clinker</t>
+  </si>
+  <si>
+    <t>Materia prima para clinker</t>
+  </si>
+  <si>
+    <t>Raw_materials_for_cement</t>
+  </si>
+  <si>
     <t>RAW_MAT_CEM</t>
   </si>
   <si>
-    <t>Suministro de materia prima para clinker</t>
+    <t>Supply of raw material for cement</t>
   </si>
   <si>
     <t>Suministro de materia prima para cemento</t>
   </si>
   <si>
-    <t>Supply of raw material for clinker</t>
-  </si>
-  <si>
-    <t>Supply of raw material for cement</t>
-  </si>
-  <si>
-    <t>Raw materials for clinker</t>
-  </si>
-  <si>
     <t>Raw materials for cement</t>
   </si>
   <si>
     <t>Materia prima para cemento</t>
   </si>
   <si>
-    <t>Materia prima para clinker</t>
-  </si>
-  <si>
-    <t>Extraction</t>
-  </si>
-  <si>
-    <t>Transformation</t>
+    <t>Clinker_production</t>
   </si>
   <si>
     <t>PROD_CLK_TRAD</t>
   </si>
   <si>
+    <t>Traditional clinker production</t>
+  </si>
+  <si>
+    <t>Producción de clinker tradicional</t>
+  </si>
+  <si>
+    <t>CLK_PROD</t>
+  </si>
+  <si>
+    <t>Clinker production</t>
+  </si>
+  <si>
+    <t>Producción de clinker</t>
+  </si>
+  <si>
+    <t>Cement_production</t>
+  </si>
+  <si>
     <t>PROD_CEM</t>
   </si>
   <si>
-    <t>Producción de clinker tradicional</t>
+    <t>Cement production</t>
   </si>
   <si>
     <t>Producción de cemento</t>
   </si>
   <si>
-    <t>Traditional clinker production</t>
-  </si>
-  <si>
-    <t>Cement production</t>
-  </si>
-  <si>
-    <t>Raw_materials_for_clinker</t>
-  </si>
-  <si>
-    <t>Raw_materials_for_cement</t>
-  </si>
-  <si>
-    <t>Clinker_production</t>
-  </si>
-  <si>
-    <t>Cement_production</t>
-  </si>
-  <si>
-    <t>CLK_PROD</t>
-  </si>
-  <si>
-    <t>Clinker production</t>
-  </si>
-  <si>
-    <t>Producción de clinker</t>
-  </si>
-  <si>
     <t>CEM_PROD</t>
+  </si>
+  <si>
+    <t>IMP_STOR</t>
+  </si>
+  <si>
+    <t>Imports or storage of Clinker</t>
+  </si>
+  <si>
+    <t>Clinker importado o almacenado</t>
+  </si>
+  <si>
+    <t>PARAFFIN</t>
+  </si>
+  <si>
+    <t>Use of Paraffin Wax</t>
+  </si>
+  <si>
+    <t>Uso de Ceras de parafina</t>
+  </si>
+  <si>
+    <t>Use_Paraffin_Wax</t>
+  </si>
+  <si>
+    <t>Use_Lubricants_oils</t>
+  </si>
+  <si>
+    <t>LUBRI_OILS</t>
+  </si>
+  <si>
+    <t>Use of Lubricants Oils</t>
+  </si>
+  <si>
+    <t>Uso de Lubricantes Aceites</t>
+  </si>
+  <si>
+    <t>Refrigeration_and_air_conditioning_HFC32</t>
+  </si>
+  <si>
+    <t>Refrigeration_and_air_conditioning_HFC125</t>
+  </si>
+  <si>
+    <t>Refrigeration_and_air_conditioning_HFC134a</t>
+  </si>
+  <si>
+    <t>Refrigeration_and_air_conditioning_HFC143a</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC32</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC125</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC134a</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC143a</t>
+  </si>
+  <si>
+    <t>Refrigeration and air conditioning HFC32</t>
+  </si>
+  <si>
+    <t>Refrigeration and air conditioning HFC125</t>
+  </si>
+  <si>
+    <t>Refrigeration and air conditioning HFC134a</t>
+  </si>
+  <si>
+    <t>Refrigeration and air conditioning HFC143a</t>
+  </si>
+  <si>
+    <t>Refrigeración y aire acondicionado HFC32</t>
+  </si>
+  <si>
+    <t>Refrigeración y aire acondicionado HFC125</t>
+  </si>
+  <si>
+    <t>Refrigeración y aire acondicionado HFC134a</t>
+  </si>
+  <si>
+    <t>Refrigeración y aire acondicionado HFC143a</t>
+  </si>
+  <si>
+    <t>Ferroalloy_production</t>
+  </si>
+  <si>
+    <t>Ferroalloy production</t>
+  </si>
+  <si>
+    <t>Produccion de ferroaleaciones</t>
+  </si>
+  <si>
+    <t>PROD_FERRO</t>
+  </si>
+  <si>
+    <t>Glass_production</t>
+  </si>
+  <si>
+    <t>GLASS_PROD</t>
+  </si>
+  <si>
+    <t>Glass production</t>
+  </si>
+  <si>
+    <t>Produccion de Vidrio</t>
+  </si>
+  <si>
+    <t>Iron_Steel_production</t>
+  </si>
+  <si>
+    <t>IRON_STEEL</t>
+  </si>
+  <si>
+    <t>Iron and Steel production</t>
+  </si>
+  <si>
+    <t>Produccion de Hierro y Acero</t>
+  </si>
+  <si>
+    <t>Lime_production_calcitic</t>
+  </si>
+  <si>
+    <t>Lime_production_dolomitic</t>
+  </si>
+  <si>
+    <t>Carbonate_ceramics</t>
+  </si>
+  <si>
+    <t>Carbonate_soda_ash</t>
+  </si>
+  <si>
+    <t>LIME_CAL_PROD</t>
+  </si>
+  <si>
+    <t>LIME_DOL_PROD</t>
+  </si>
+  <si>
+    <t>CARBONATE_CERAMICS</t>
+  </si>
+  <si>
+    <t>CARBONATE_ASH</t>
+  </si>
+  <si>
+    <t>Carbonate ceramics</t>
+  </si>
+  <si>
+    <t>Carbonate soda ash</t>
+  </si>
+  <si>
+    <t>Lime production calcitic</t>
+  </si>
+  <si>
+    <t>Lime production dolomitic</t>
+  </si>
+  <si>
+    <t>Produccion de Cal Calcítica</t>
+  </si>
+  <si>
+    <t>Produccion de Dolomítica</t>
+  </si>
+  <si>
+    <t>Carbonato para cerámicas</t>
+  </si>
+  <si>
+    <t>Carbonato Soda Ash</t>
   </si>
 </sst>
 </file>
@@ -253,7 +421,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -280,12 +448,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -360,6 +534,81 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -423,14 +672,280 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -439,7 +954,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -450,56 +965,168 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -781,24 +1408,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89413C42-1AB9-45A0-982B-1FD917C59C4F}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -811,133 +1438,623 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <tabColor theme="7"/>
+    <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.42578125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="63.85546875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="56.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.77734375" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="42.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.44140625" customWidth="1"/>
+    <col min="8" max="8" width="66.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="66.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>9</v>
+      <c r="E1" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="C4" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
+      <c r="D4" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" s="32" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>29</v>
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="J5" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="K5" s="41" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>28</v>
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="H6" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="I6" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="J6" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="K6" s="41" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="J7" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="K7" s="41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="H8" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="J8" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="K8" s="40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="H9" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="K9" s="40" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="J10" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="41" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" s="41" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12" s="41" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="K13" s="43" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="K14" s="44" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="H15" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="K15" s="48" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="K16" s="48" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="I17" s="55" t="s">
+        <v>65</v>
+      </c>
+      <c r="J17" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17" s="54" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K2" xr:uid="{A8645EFF-8284-4A3D-B8FA-E0EBC6D612AC}"/>
+  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -945,27 +2062,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3D3F466-5712-4E2F-BFB1-24D1EC490CA3}">
   <sheetPr>
-    <tabColor theme="7"/>
+    <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="43.85546875" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" customWidth="1"/>
-    <col min="7" max="8" width="45.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="56.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="39.5703125" customWidth="1"/>
-    <col min="14" max="14" width="41.7109375" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" customWidth="1"/>
+    <col min="4" max="4" width="55.21875" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" customWidth="1"/>
+    <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.5546875" customWidth="1"/>
+    <col min="8" max="8" width="28.109375" customWidth="1"/>
+    <col min="9" max="9" width="19.109375" customWidth="1"/>
+    <col min="10" max="10" width="23.6640625" customWidth="1"/>
+    <col min="11" max="11" width="24.44140625" customWidth="1"/>
+    <col min="12" max="12" width="19.88671875" customWidth="1"/>
+    <col min="13" max="13" width="26.5546875" customWidth="1"/>
+    <col min="14" max="14" width="26.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -976,174 +2094,174 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="C2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>16</v>
+      <c r="D2" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" s="22" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="5" t="s">
+    <row r="3" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>42</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="N2" s="18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>41</v>
       </c>
       <c r="E3" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="N3" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K3" s="18" t="s">
+      <c r="K4" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="N4" s="28" t="s">
         <v>45</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="N3" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" s="18" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1390,7 +2508,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EF493FB-B434-4D4B-A7D7-2C8A0CF68AF6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{403D9D63-26D9-4EB4-B4C2-560BB6B22FD3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -1398,9 +2516,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D613775-AEB8-42B1-B694-C2B7EFF16AB3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4042F90-E19F-4C3E-B201-844825442CAF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5D07BF8-9886-43B9-8372-4EBD33D21CF0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF6E3E9D-60C7-4643-91EF-AD66852F9C90}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0d55314f-45f1-40c9-9fce-63556e193d03"/>
+    <ds:schemaRef ds:uri="48eed89a-7418-4977-ae3a-838f0fac8ec5"/>
+    <ds:schemaRef ds:uri="416d42ac-85ec-40c4-8054-6c816fd4b6a7"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>